--- a/docs/智能食堂系统开发计划任务清单.xlsx
+++ b/docs/智能食堂系统开发计划任务清单.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5ecb4ed35d1e4fed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务清单" sheetId="2" r:id="R6c47f50876944bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键流程检查" sheetId="3" r:id="Rd621344c37a14015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="4" r:id="R87e2df97cb06424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7e6aa362dbad4101"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务清单" sheetId="2" r:id="R05b11af718ee453d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键流程检查" sheetId="3" r:id="R3c0ae691e2704c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="4" r:id="Re4c291c6f2404c3d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3691,7 +3691,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bbae95d358d432e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d716ba9611a4f57"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -6932,11 +6932,15 @@
       <x:c r="I82" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J82" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K82" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J82" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K82" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L82" s="9"/>
       <x:c r="M82" s="9"/>
@@ -6971,11 +6975,15 @@
       <x:c r="I83" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J83" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K83" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J83" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K83" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L83" s="9"/>
       <x:c r="M83" s="9"/>
@@ -7010,11 +7018,15 @@
       <x:c r="I84" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J84" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K84" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J84" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K84" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L84" s="9"/>
       <x:c r="M84" s="9"/>
@@ -7049,11 +7061,15 @@
       <x:c r="I85" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J85" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K85" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J85" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K85" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L85" s="9"/>
       <x:c r="M85" s="9"/>
@@ -7088,11 +7104,15 @@
       <x:c r="I86" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J86" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K86" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J86" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☐</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K86" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">进行中</x:t>
+        </x:is>
       </x:c>
       <x:c r="L86" s="9"/>
       <x:c r="M86" s="9"/>
@@ -7127,11 +7147,15 @@
       <x:c r="I87" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J87" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K87" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J87" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K87" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L87" s="9"/>
       <x:c r="M87" s="9"/>
@@ -7166,11 +7190,15 @@
       <x:c r="I88" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J88" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K88" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J88" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☑</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K88" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="L88" s="9"/>
       <x:c r="M88" s="9"/>
@@ -7205,13 +7233,15 @@
       <x:c r="I89" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J89" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K89" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L89" s="9"/>
+      <x:c r="J89" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K89" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L89" s="9" t="str">
+        <x:v>已实现商家接单/拒单/出餐接口，含状态校验、商家归属校验、接单超时、库存释放、pickup 队列流转与单测。</x:v>
+      </x:c>
       <x:c r="M89" s="9"/>
       <x:c r="N89" s="9"/>
       <x:c r="O89" s="7"/>
@@ -7244,13 +7274,15 @@
       <x:c r="I90" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J90" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K90" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L90" s="9"/>
+      <x:c r="J90" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K90" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L90" s="9" t="str">
+        <x:v>已实现 PAID 拒单取消并调用 menu-service 释放库存。</x:v>
+      </x:c>
       <x:c r="M90" s="9"/>
       <x:c r="N90" s="9"/>
       <x:c r="O90" s="7"/>
@@ -7283,13 +7315,15 @@
       <x:c r="I91" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J91" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K91" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L91" s="9"/>
+      <x:c r="J91" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K91" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L91" s="9" t="str">
+        <x:v>已实现 PREPARING 出餐转 READY，调用 pickup-service 转待取餐、生成二维码并自动叫号。</x:v>
+      </x:c>
       <x:c r="M91" s="9"/>
       <x:c r="N91" s="9"/>
       <x:c r="O91" s="7"/>
@@ -7322,13 +7356,15 @@
       <x:c r="I92" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J92" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K92" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L92" s="9"/>
+      <x:c r="J92" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K92" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L92" s="9" t="str">
+        <x:v>已实现 /internal/order/{orderId}/complete：READY 幂等同步 COMPLETED，调用 menu-service consume，并由 pickup 核销成功后同步。</x:v>
+      </x:c>
       <x:c r="M92" s="9"/>
       <x:c r="N92" s="9"/>
       <x:c r="O92" s="7"/>
@@ -7361,13 +7397,15 @@
       <x:c r="I93" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J93" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K93" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L93" s="9"/>
+      <x:c r="J93" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K93" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L93" s="9" t="str">
+        <x:v>已实现 /api/admin/order/config：查询刷新 Redis 缓存，修改正整数分钟配置并记录 updatedBy。</x:v>
+      </x:c>
       <x:c r="M93" s="9"/>
       <x:c r="N93" s="9"/>
       <x:c r="O93" s="7"/>
@@ -7400,11 +7438,15 @@
       <x:c r="I94" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J94" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K94" s="8" t="s">
-        <x:v>192</x:v>
+      <x:c r="J94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">☐</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未开始</x:t>
+        </x:is>
       </x:c>
       <x:c r="L94" s="9"/>
       <x:c r="M94" s="9"/>
@@ -7439,13 +7481,15 @@
       <x:c r="I95" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J95" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K95" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L95" s="9"/>
+      <x:c r="J95" s="8" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="K95" s="8" t="str">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="L95" s="9" t="str">
+        <x:v>已补商家流程、核销同步、订单配置、RocketMQ 超时消息、定时扫描兜底单测；Seata 代码配置已准备，等待容器环境真联调。</x:v>
+      </x:c>
       <x:c r="M95" s="9"/>
       <x:c r="N95" s="9"/>
       <x:c r="O95" s="7"/>
@@ -7478,13 +7522,15 @@
       <x:c r="I96" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J96" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K96" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L96" s="9"/>
+      <x:c r="J96" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K96" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L96" s="9" t="str">
+        <x:v>已配置 user/menu/order/pickup/admin/ws 基础路由，order 管理配置路由已补齐。</x:v>
+      </x:c>
       <x:c r="M96" s="9"/>
       <x:c r="N96" s="9"/>
       <x:c r="O96" s="7"/>
@@ -7517,13 +7563,15 @@
       <x:c r="I97" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J97" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K97" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L97" s="9"/>
+      <x:c r="J97" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K97" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L97" s="9" t="str">
+        <x:v>已实现方法级白名单：登录注册、可售菜单、公开分类/菜品详情、公开队列/大屏 ws。</x:v>
+      </x:c>
       <x:c r="M97" s="9"/>
       <x:c r="N97" s="9"/>
       <x:c r="O97" s="7"/>
@@ -7556,13 +7604,15 @@
       <x:c r="I98" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J98" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K98" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L98" s="9"/>
+      <x:c r="J98" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K98" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L98" s="9" t="str">
+        <x:v>已实现 AuthGlobalFilter：校验 Bearer token、签名、过期、Redis 黑名单，并注入 X-User-*。</x:v>
+      </x:c>
       <x:c r="M98" s="9"/>
       <x:c r="N98" s="9"/>
       <x:c r="O98" s="7"/>
@@ -7595,13 +7645,15 @@
       <x:c r="I99" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J99" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K99" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L99" s="9"/>
+      <x:c r="J99" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K99" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L99" s="9" t="str">
+        <x:v>已实现 ADMIN/MERCHANT 路径角色拦截；普通受保护接口交由后端做细粒度归属校验。</x:v>
+      </x:c>
       <x:c r="M99" s="9"/>
       <x:c r="N99" s="9"/>
       <x:c r="O99" s="7"/>
@@ -7634,13 +7686,15 @@
       <x:c r="I100" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J100" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K100" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L100" s="9"/>
+      <x:c r="J100" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K100" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L100" s="9" t="str">
+        <x:v>已实现 Redis + Lua 令牌桶限流：IP 100 req/s、用户 50 req/s、敏感接口 5 req/min，超限返回 429。</x:v>
+      </x:c>
       <x:c r="M100" s="9"/>
       <x:c r="N100" s="9"/>
       <x:c r="O100" s="7"/>
@@ -7673,13 +7727,15 @@
       <x:c r="I101" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J101" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K101" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L101" s="9"/>
+      <x:c r="J101" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K101" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L101" s="9" t="str">
+        <x:v>已配置 Gateway 全局 CORS，允许 Authorization、Content-Type、X-Idempotent-Key 和 WebSocket 相关跨域请求。</x:v>
+      </x:c>
       <x:c r="M101" s="9"/>
       <x:c r="N101" s="9"/>
       <x:c r="O101" s="7"/>
@@ -7712,13 +7768,15 @@
       <x:c r="I102" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J102" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K102" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L102" s="9"/>
+      <x:c r="J102" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K102" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L102" s="9" t="str">
+        <x:v>已配置 /ws/** 转发到 pickup-service，并在鉴权白名单中放行大屏 WebSocket。</x:v>
+      </x:c>
       <x:c r="M102" s="9"/>
       <x:c r="N102" s="9"/>
       <x:c r="O102" s="7"/>
@@ -7751,13 +7809,15 @@
       <x:c r="I103" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J103" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K103" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L103" s="9"/>
+      <x:c r="J103" s="8" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="K103" s="8" t="str">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="L103" s="9" t="str">
+        <x:v>已补 AuthGlobalFilter 与 RateLimitGlobalFilter 单测；剩余真实服务路由联调。</x:v>
+      </x:c>
       <x:c r="M103" s="9"/>
       <x:c r="N103" s="9"/>
       <x:c r="O103" s="7"/>
@@ -7790,13 +7850,15 @@
       <x:c r="I104" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J104" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K104" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L104" s="9"/>
+      <x:c r="J104" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K104" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L104" s="9" t="str">
+        <x:v>已直接接入真实业务 RocketMQ 发送/消费链路，替代临时 demo。</x:v>
+      </x:c>
       <x:c r="M104" s="9"/>
       <x:c r="N104" s="9"/>
       <x:c r="O104" s="7"/>
@@ -7829,13 +7891,15 @@
       <x:c r="I105" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J105" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K105" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L105" s="9"/>
+      <x:c r="J105" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K105" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L105" s="9" t="str">
+        <x:v>创建订单成功后发送 pay_timeout 延迟消息。</x:v>
+      </x:c>
       <x:c r="M105" s="9"/>
       <x:c r="N105" s="9"/>
       <x:c r="O105" s="7"/>
@@ -7868,13 +7932,15 @@
       <x:c r="I106" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J106" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K106" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L106" s="9"/>
+      <x:c r="J106" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K106" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L106" s="9" t="str">
+        <x:v>支付成功后发送 accept_timeout 延迟消息。</x:v>
+      </x:c>
       <x:c r="M106" s="9"/>
       <x:c r="N106" s="9"/>
       <x:c r="O106" s="7"/>
@@ -7907,13 +7973,15 @@
       <x:c r="I107" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J107" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K107" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L107" s="9"/>
+      <x:c r="J107" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K107" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L107" s="9" t="str">
+        <x:v>已实现 order-timeout 消费者，消费时二次检查状态和当前配置，重复/已流转消息会忽略。</x:v>
+      </x:c>
       <x:c r="M107" s="9"/>
       <x:c r="N107" s="9"/>
       <x:c r="O107" s="7"/>
@@ -7946,13 +8014,15 @@
       <x:c r="I108" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J108" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K108" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L108" s="9"/>
+      <x:c r="J108" s="8" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K108" s="8" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="L108" s="9" t="str">
+        <x:v>已实现每分钟超时扫描兜底：Redis 锁防多实例重复，扫描 PENDING_PAY/PAID 超时订单并复用取消逻辑。</x:v>
+      </x:c>
       <x:c r="M108" s="9"/>
       <x:c r="N108" s="9"/>
       <x:c r="O108" s="7"/>
@@ -7985,13 +8055,15 @@
       <x:c r="I109" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J109" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K109" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L109" s="9"/>
+      <x:c r="J109" s="8" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="K109" s="8" t="str">
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="L109" s="9" t="str">
+        <x:v>代码侧已补 Seata 事务分组、AT 数据源代理配置并对齐 Seata Server 版本；当前环境缺少 docker/podman/colima，暂无法启动基础组件做真联调。见 docs/Seata联调说明.md。</x:v>
+      </x:c>
       <x:c r="M109" s="9"/>
       <x:c r="N109" s="9"/>
       <x:c r="O109" s="7"/>
@@ -8024,13 +8096,15 @@
       <x:c r="I110" s="8">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J110" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="K110" s="8" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="L110" s="9"/>
+      <x:c r="J110" s="8" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="K110" s="8" t="str">
+        <x:v>阻塞</x:v>
+      </x:c>
+      <x:c r="L110" s="9" t="str">
+        <x:v>同上：需可用容器环境后验证库存不足/人为异常时 order_db 和 menu_db 一致回滚。</x:v>
+      </x:c>
       <x:c r="M110" s="9"/>
       <x:c r="N110" s="9"/>
       <x:c r="O110" s="7"/>
@@ -10213,7 +10287,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcb28752841e4da7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29262baced3f43f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10274,13 +10348,15 @@
       <x:c r="E2" s="4" t="s">
         <x:v>742</x:v>
       </x:c>
-      <x:c r="F2" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H2" s="4"/>
+      <x:c r="F2" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="str">
+        <x:v>后端主流程已闭环到 COMPLETED：下单、支付、接单、出餐、核销同步、库存消费均已实现，待端到端联调。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="4">
@@ -10370,13 +10446,15 @@
       <x:c r="E6" s="4" t="s">
         <x:v>751</x:v>
       </x:c>
-      <x:c r="F6" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H6" s="4"/>
+      <x:c r="F6" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H6" s="4" t="str">
+        <x:v>后端接口已实现：PAID 拒单取消并释放库存，待后续联调复核。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="4">
@@ -10418,13 +10496,15 @@
       <x:c r="E8" s="4" t="s">
         <x:v>759</x:v>
       </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H8" s="4"/>
+      <x:c r="F8" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H8" s="4" t="str">
+        <x:v>接单后调用 pickup 入制作中队列并生成取餐号，待大屏联调复核。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="4">
@@ -10442,13 +10522,15 @@
       <x:c r="E9" s="4" t="s">
         <x:v>762</x:v>
       </x:c>
-      <x:c r="F9" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G9" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H9" s="4"/>
+      <x:c r="F9" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>出餐后调用 pickup 转待取餐、生成二维码并自动叫号，待大屏联调复核。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
       <x:c r="A10" s="4">
@@ -10490,13 +10572,15 @@
       <x:c r="E11" s="4" t="s">
         <x:v>769</x:v>
       </x:c>
-      <x:c r="F11" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G11" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H11" s="4"/>
+      <x:c r="F11" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="str">
+        <x:v>扫码核销路径已同步 order-service 完成订单，并从待取餐队列移除。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
       <x:c r="A12" s="4">
@@ -10514,13 +10598,15 @@
       <x:c r="E12" s="4" t="s">
         <x:v>772</x:v>
       </x:c>
-      <x:c r="F12" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G12" s="4" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H12" s="4"/>
+      <x:c r="F12" s="4" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="G12" s="4" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="H12" s="4" t="str">
+        <x:v>手动取餐码核销走同一同步逻辑。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
       <x:c r="A13" s="4">
@@ -10687,7 +10773,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cdadccf92774736"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90d5222f57a045cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/智能食堂系统开发计划任务清单.xlsx
+++ b/docs/智能食堂系统开发计划任务清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhongjiating/Projects/smart-canteen/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\smart-canteen\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB92B066-7B57-5044-85A3-63EF36A24A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCB2EC5-D29B-4C89-9583-BC5BB6B99912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -1613,9 +1613,6 @@
     <t>公共能力</t>
   </si>
   <si>
-    <t>创建四个 Vue 3 工程</t>
-  </si>
-  <si>
     <t>user-web、merchant-web、admin-web、screen-web；统一 Vite 配置</t>
   </si>
   <si>
@@ -2595,6 +2592,21 @@
   </si>
   <si>
     <t>手动取餐码核销走同一同步逻辑。</t>
+  </si>
+  <si>
+    <r>
+      <t>创建四个 Vue 3 工程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（修改为单个）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2605,7 +2617,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2644,6 +2656,12 @@
       <b/>
       <sz val="11"/>
       <name val="宋体-简 常规体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3021,14 +3039,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
     <col min="2" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="1"/>
+    <col min="8" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="34" customHeight="1">
+    <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3040,7 +3058,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="3" spans="1:8" ht="26.75" customHeight="1">
+    <row r="3" spans="1:8" ht="26.85" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3057,7 +3075,7 @@
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" ht="202.75" customHeight="1">
+    <row r="4" spans="1:8" ht="202.7" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -3075,13 +3093,13 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:8" ht="26.75" customHeight="1">
+    <row r="5" spans="1:8" ht="26.85" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(任务清单!$J$2:$J$165,"☑")</f>
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -3091,7 +3109,7 @@
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:8" ht="47" customHeight="1">
+    <row r="6" spans="1:8" ht="47.1" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -3107,7 +3125,7 @@
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:8" ht="47" customHeight="1">
+    <row r="7" spans="1:8" ht="47.1" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -3123,7 +3141,7 @@
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:8" ht="26.75" customHeight="1">
+    <row r="8" spans="1:8" ht="26.85" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -3139,13 +3157,13 @@
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:8" ht="47" customHeight="1">
+    <row r="9" spans="1:8" ht="47.1" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5">
         <f>IF(B4=0,0,B5/B4)</f>
-        <v>0.61585365853658536</v>
+        <v>0.67682926829268297</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>17</v>
@@ -3155,7 +3173,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
     </row>
-    <row r="12" spans="1:8" ht="26.75" customHeight="1">
+    <row r="12" spans="1:8" ht="26.85" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -3178,7 +3196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="26.75" customHeight="1">
+    <row r="13" spans="1:8" ht="26.85" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -3207,7 +3225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="26.75" customHeight="1">
+    <row r="14" spans="1:8" ht="26.85" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>26</v>
       </c>
@@ -3236,7 +3254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="26.75" customHeight="1">
+    <row r="15" spans="1:8" ht="26.85" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>27</v>
       </c>
@@ -3265,7 +3283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="26.75" customHeight="1">
+    <row r="16" spans="1:8" ht="26.85" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -3294,7 +3312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="26.75" customHeight="1">
+    <row r="17" spans="1:7" ht="26.85" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>29</v>
       </c>
@@ -3323,7 +3341,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="26.75" customHeight="1">
+    <row r="18" spans="1:7" ht="26.85" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
@@ -3352,7 +3370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="26.75" customHeight="1">
+    <row r="19" spans="1:7" ht="26.85" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>31</v>
       </c>
@@ -3381,7 +3399,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="26.75" customHeight="1">
+    <row r="20" spans="1:7" ht="26.85" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>32</v>
       </c>
@@ -3410,7 +3428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="26.75" customHeight="1">
+    <row r="21" spans="1:7" ht="26.85" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
@@ -3439,7 +3457,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="26.75" customHeight="1">
+    <row r="22" spans="1:7" ht="26.85" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>34</v>
       </c>
@@ -3468,7 +3486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="26.75" customHeight="1">
+    <row r="23" spans="1:7" ht="26.85" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>35</v>
       </c>
@@ -3478,11 +3496,11 @@
       </c>
       <c r="C23" s="4">
         <f>COUNTIFS(任务清单!$B$2:$B$165,A23,任务清单!$J$2:$J$165,"☑")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" s="5">
         <f t="shared" si="0"/>
-        <v>0.77777777777777779</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
         <f>COUNTIFS(任务清单!$B$2:$B$165,A23,任务清单!$K$2:$K$165,"进行中")</f>
@@ -3497,7 +3515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="26.75" customHeight="1">
+    <row r="24" spans="1:7" ht="26.85" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>36</v>
       </c>
@@ -3507,11 +3525,11 @@
       </c>
       <c r="C24" s="4">
         <f>COUNTIFS(任务清单!$B$2:$B$165,A24,任务清单!$J$2:$J$165,"☑")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D24" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="4">
         <f>COUNTIFS(任务清单!$B$2:$B$165,A24,任务清单!$K$2:$K$165,"进行中")</f>
@@ -3526,7 +3544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="26.75" customHeight="1">
+    <row r="25" spans="1:7" ht="26.85" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
@@ -3555,7 +3573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="26.75" customHeight="1">
+    <row r="26" spans="1:7" ht="26.85" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
@@ -3584,7 +3602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="26.75" customHeight="1">
+    <row r="27" spans="1:7" ht="26.85" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>39</v>
       </c>
@@ -3675,7 +3693,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O165"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3692,7 +3710,7 @@
     <col min="15" max="15" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="26.75" customHeight="1">
+    <row r="1" spans="1:15" ht="26.85" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
@@ -3739,7 +3757,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="47" customHeight="1">
+    <row r="2" spans="1:15" ht="47.1" customHeight="1">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -3778,7 +3796,7 @@
       <c r="N2" s="9"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:15" ht="47" customHeight="1">
+    <row r="3" spans="1:15" ht="47.1" customHeight="1">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -3817,7 +3835,7 @@
       <c r="N3" s="9"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="47" customHeight="1">
+    <row r="4" spans="1:15" ht="47.1" customHeight="1">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -3856,7 +3874,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="47" customHeight="1">
+    <row r="5" spans="1:15" ht="47.1" customHeight="1">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -3895,7 +3913,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" ht="47" customHeight="1">
+    <row r="6" spans="1:15" ht="47.1" customHeight="1">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -3909,7 +3927,7 @@
         <v>78</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>79</v>
@@ -3934,7 +3952,7 @@
       <c r="N6" s="9"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" ht="26.75" customHeight="1">
+    <row r="7" spans="1:15" ht="26.85" customHeight="1">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -3973,7 +3991,7 @@
       <c r="N7" s="9"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="26.75" customHeight="1">
+    <row r="8" spans="1:15" ht="26.85" customHeight="1">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -4012,7 +4030,7 @@
       <c r="N8" s="9"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="26.75" customHeight="1">
+    <row r="9" spans="1:15" ht="26.85" customHeight="1">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -4051,7 +4069,7 @@
       <c r="N9" s="9"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="26.75" customHeight="1">
+    <row r="10" spans="1:15" ht="26.85" customHeight="1">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -4090,7 +4108,7 @@
       <c r="N10" s="9"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="26.75" customHeight="1">
+    <row r="11" spans="1:15" ht="26.85" customHeight="1">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -4129,7 +4147,7 @@
       <c r="N11" s="9"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" ht="26.75" customHeight="1">
+    <row r="12" spans="1:15" ht="26.85" customHeight="1">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -4168,7 +4186,7 @@
       <c r="N12" s="9"/>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="1:15" ht="26.75" customHeight="1">
+    <row r="13" spans="1:15" ht="26.85" customHeight="1">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -4207,7 +4225,7 @@
       <c r="N13" s="9"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="1:15" ht="47" customHeight="1">
+    <row r="14" spans="1:15" ht="47.1" customHeight="1">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -4246,7 +4264,7 @@
       <c r="N14" s="9"/>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="1:15" ht="26.75" customHeight="1">
+    <row r="15" spans="1:15" ht="26.85" customHeight="1">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -4285,7 +4303,7 @@
       <c r="N15" s="9"/>
       <c r="O15" s="7"/>
     </row>
-    <row r="16" spans="1:15" ht="26.75" customHeight="1">
+    <row r="16" spans="1:15" ht="26.85" customHeight="1">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -4324,7 +4342,7 @@
       <c r="N16" s="9"/>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="1:15" ht="26.75" customHeight="1">
+    <row r="17" spans="1:15" ht="26.85" customHeight="1">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -4363,7 +4381,7 @@
       <c r="N17" s="9"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="1:15" ht="70.25" customHeight="1">
+    <row r="18" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -4402,7 +4420,7 @@
       <c r="N18" s="9"/>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="1:15" ht="26.75" customHeight="1">
+    <row r="19" spans="1:15" ht="26.85" customHeight="1">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -4441,7 +4459,7 @@
       <c r="N19" s="9"/>
       <c r="O19" s="7"/>
     </row>
-    <row r="20" spans="1:15" ht="70.25" customHeight="1">
+    <row r="20" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -4480,7 +4498,7 @@
       <c r="N20" s="9"/>
       <c r="O20" s="7"/>
     </row>
-    <row r="21" spans="1:15" ht="26.75" customHeight="1">
+    <row r="21" spans="1:15" ht="26.85" customHeight="1">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -4519,7 +4537,7 @@
       <c r="N21" s="9"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15" ht="70.25" customHeight="1">
+    <row r="22" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -4533,7 +4551,7 @@
         <v>147</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>145</v>
@@ -4558,7 +4576,7 @@
       <c r="N22" s="9"/>
       <c r="O22" s="7"/>
     </row>
-    <row r="23" spans="1:15" ht="47" customHeight="1">
+    <row r="23" spans="1:15" ht="47.1" customHeight="1">
       <c r="A23" s="7">
         <v>22</v>
       </c>
@@ -4597,7 +4615,7 @@
       <c r="N23" s="9"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" ht="47" customHeight="1">
+    <row r="24" spans="1:15" ht="47.1" customHeight="1">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -4636,7 +4654,7 @@
       <c r="N24" s="9"/>
       <c r="O24" s="7"/>
     </row>
-    <row r="25" spans="1:15" ht="26.75" customHeight="1">
+    <row r="25" spans="1:15" ht="26.85" customHeight="1">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -4675,7 +4693,7 @@
       <c r="N25" s="9"/>
       <c r="O25" s="7"/>
     </row>
-    <row r="26" spans="1:15" ht="70.25" customHeight="1">
+    <row r="26" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A26" s="7">
         <v>25</v>
       </c>
@@ -4689,7 +4707,7 @@
         <v>160</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>161</v>
@@ -4714,7 +4732,7 @@
       <c r="N26" s="9"/>
       <c r="O26" s="7"/>
     </row>
-    <row r="27" spans="1:15" ht="47" customHeight="1">
+    <row r="27" spans="1:15" ht="47.1" customHeight="1">
       <c r="A27" s="7">
         <v>26</v>
       </c>
@@ -4755,7 +4773,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="26.75" customHeight="1">
+    <row r="28" spans="1:15" ht="26.85" customHeight="1">
       <c r="A28" s="7">
         <v>27</v>
       </c>
@@ -4794,7 +4812,7 @@
       <c r="N28" s="9"/>
       <c r="O28" s="7"/>
     </row>
-    <row r="29" spans="1:15" ht="26.75" customHeight="1">
+    <row r="29" spans="1:15" ht="26.85" customHeight="1">
       <c r="A29" s="7">
         <v>28</v>
       </c>
@@ -4833,7 +4851,7 @@
       <c r="N29" s="9"/>
       <c r="O29" s="7"/>
     </row>
-    <row r="30" spans="1:15" ht="26.75" customHeight="1">
+    <row r="30" spans="1:15" ht="26.85" customHeight="1">
       <c r="A30" s="7">
         <v>29</v>
       </c>
@@ -4872,7 +4890,7 @@
       <c r="N30" s="9"/>
       <c r="O30" s="7"/>
     </row>
-    <row r="31" spans="1:15" ht="70.25" customHeight="1">
+    <row r="31" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A31" s="7">
         <v>30</v>
       </c>
@@ -4911,7 +4929,7 @@
       <c r="N31" s="9"/>
       <c r="O31" s="7"/>
     </row>
-    <row r="32" spans="1:15" ht="26.75" customHeight="1">
+    <row r="32" spans="1:15" ht="26.85" customHeight="1">
       <c r="A32" s="7">
         <v>31</v>
       </c>
@@ -4950,7 +4968,7 @@
       <c r="N32" s="9"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15" ht="26.75" customHeight="1">
+    <row r="33" spans="1:15" ht="26.85" customHeight="1">
       <c r="A33" s="7">
         <v>32</v>
       </c>
@@ -4989,7 +5007,7 @@
       <c r="N33" s="9"/>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:15" ht="47" customHeight="1">
+    <row r="34" spans="1:15" ht="47.1" customHeight="1">
       <c r="A34" s="7">
         <v>33</v>
       </c>
@@ -5028,7 +5046,7 @@
       <c r="N34" s="9"/>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:15" ht="47" customHeight="1">
+    <row r="35" spans="1:15" ht="47.1" customHeight="1">
       <c r="A35" s="7">
         <v>34</v>
       </c>
@@ -5067,7 +5085,7 @@
       <c r="N35" s="9"/>
       <c r="O35" s="7"/>
     </row>
-    <row r="36" spans="1:15" ht="70.25" customHeight="1">
+    <row r="36" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -5106,7 +5124,7 @@
       <c r="N36" s="9"/>
       <c r="O36" s="7"/>
     </row>
-    <row r="37" spans="1:15" ht="47" customHeight="1">
+    <row r="37" spans="1:15" ht="47.1" customHeight="1">
       <c r="A37" s="7">
         <v>36</v>
       </c>
@@ -5145,7 +5163,7 @@
       <c r="N37" s="9"/>
       <c r="O37" s="7"/>
     </row>
-    <row r="38" spans="1:15" ht="47" customHeight="1">
+    <row r="38" spans="1:15" ht="47.1" customHeight="1">
       <c r="A38" s="7">
         <v>37</v>
       </c>
@@ -5184,7 +5202,7 @@
       <c r="N38" s="9"/>
       <c r="O38" s="7"/>
     </row>
-    <row r="39" spans="1:15" ht="70.25" customHeight="1">
+    <row r="39" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A39" s="7">
         <v>38</v>
       </c>
@@ -5223,7 +5241,7 @@
       <c r="N39" s="9"/>
       <c r="O39" s="7"/>
     </row>
-    <row r="40" spans="1:15" ht="26.75" customHeight="1">
+    <row r="40" spans="1:15" ht="26.85" customHeight="1">
       <c r="A40" s="7">
         <v>39</v>
       </c>
@@ -5262,7 +5280,7 @@
       <c r="N40" s="9"/>
       <c r="O40" s="7"/>
     </row>
-    <row r="41" spans="1:15" ht="26.75" customHeight="1">
+    <row r="41" spans="1:15" ht="26.85" customHeight="1">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -5301,7 +5319,7 @@
       <c r="N41" s="9"/>
       <c r="O41" s="7"/>
     </row>
-    <row r="42" spans="1:15" ht="26.75" customHeight="1">
+    <row r="42" spans="1:15" ht="26.85" customHeight="1">
       <c r="A42" s="7">
         <v>41</v>
       </c>
@@ -5340,7 +5358,7 @@
       <c r="N42" s="9"/>
       <c r="O42" s="7"/>
     </row>
-    <row r="43" spans="1:15" ht="70.25" customHeight="1">
+    <row r="43" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A43" s="7">
         <v>42</v>
       </c>
@@ -5379,7 +5397,7 @@
       <c r="N43" s="9"/>
       <c r="O43" s="7"/>
     </row>
-    <row r="44" spans="1:15" ht="47" customHeight="1">
+    <row r="44" spans="1:15" ht="47.1" customHeight="1">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -5418,7 +5436,7 @@
       <c r="N44" s="9"/>
       <c r="O44" s="7"/>
     </row>
-    <row r="45" spans="1:15" ht="47" customHeight="1">
+    <row r="45" spans="1:15" ht="47.1" customHeight="1">
       <c r="A45" s="7">
         <v>44</v>
       </c>
@@ -5457,7 +5475,7 @@
       <c r="N45" s="9"/>
       <c r="O45" s="7"/>
     </row>
-    <row r="46" spans="1:15" ht="47" customHeight="1">
+    <row r="46" spans="1:15" ht="47.1" customHeight="1">
       <c r="A46" s="7">
         <v>45</v>
       </c>
@@ -5496,7 +5514,7 @@
       <c r="N46" s="9"/>
       <c r="O46" s="7"/>
     </row>
-    <row r="47" spans="1:15" ht="26.75" customHeight="1">
+    <row r="47" spans="1:15" ht="26.85" customHeight="1">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -5535,7 +5553,7 @@
       <c r="N47" s="9"/>
       <c r="O47" s="7"/>
     </row>
-    <row r="48" spans="1:15" ht="47" customHeight="1">
+    <row r="48" spans="1:15" ht="47.1" customHeight="1">
       <c r="A48" s="7">
         <v>47</v>
       </c>
@@ -5574,7 +5592,7 @@
       <c r="N48" s="9"/>
       <c r="O48" s="7"/>
     </row>
-    <row r="49" spans="1:15" ht="26.75" customHeight="1">
+    <row r="49" spans="1:15" ht="26.85" customHeight="1">
       <c r="A49" s="7">
         <v>48</v>
       </c>
@@ -5613,7 +5631,7 @@
       <c r="N49" s="9"/>
       <c r="O49" s="7"/>
     </row>
-    <row r="50" spans="1:15" ht="47" customHeight="1">
+    <row r="50" spans="1:15" ht="47.1" customHeight="1">
       <c r="A50" s="7">
         <v>49</v>
       </c>
@@ -5652,7 +5670,7 @@
       <c r="N50" s="9"/>
       <c r="O50" s="7"/>
     </row>
-    <row r="51" spans="1:15" ht="47" customHeight="1">
+    <row r="51" spans="1:15" ht="47.1" customHeight="1">
       <c r="A51" s="7">
         <v>50</v>
       </c>
@@ -5691,7 +5709,7 @@
       <c r="N51" s="9"/>
       <c r="O51" s="7"/>
     </row>
-    <row r="52" spans="1:15" ht="26.75" customHeight="1">
+    <row r="52" spans="1:15" ht="26.85" customHeight="1">
       <c r="A52" s="7">
         <v>51</v>
       </c>
@@ -5730,7 +5748,7 @@
       <c r="N52" s="9"/>
       <c r="O52" s="7"/>
     </row>
-    <row r="53" spans="1:15" ht="26.75" customHeight="1">
+    <row r="53" spans="1:15" ht="26.85" customHeight="1">
       <c r="A53" s="7">
         <v>52</v>
       </c>
@@ -5769,7 +5787,7 @@
       <c r="N53" s="9"/>
       <c r="O53" s="7"/>
     </row>
-    <row r="54" spans="1:15" ht="26.75" customHeight="1">
+    <row r="54" spans="1:15" ht="26.85" customHeight="1">
       <c r="A54" s="7">
         <v>53</v>
       </c>
@@ -5808,7 +5826,7 @@
       <c r="N54" s="9"/>
       <c r="O54" s="7"/>
     </row>
-    <row r="55" spans="1:15" ht="47" customHeight="1">
+    <row r="55" spans="1:15" ht="47.1" customHeight="1">
       <c r="A55" s="7">
         <v>54</v>
       </c>
@@ -5819,7 +5837,7 @@
         <v>232</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>288</v>
@@ -5847,7 +5865,7 @@
       <c r="N55" s="9"/>
       <c r="O55" s="7"/>
     </row>
-    <row r="56" spans="1:15" ht="47" customHeight="1">
+    <row r="56" spans="1:15" ht="47.1" customHeight="1">
       <c r="A56" s="7">
         <v>55</v>
       </c>
@@ -5858,7 +5876,7 @@
         <v>41</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>291</v>
@@ -5886,7 +5904,7 @@
       <c r="N56" s="9"/>
       <c r="O56" s="7"/>
     </row>
-    <row r="57" spans="1:15" ht="47" customHeight="1">
+    <row r="57" spans="1:15" ht="47.1" customHeight="1">
       <c r="A57" s="7">
         <v>56</v>
       </c>
@@ -5925,7 +5943,7 @@
       <c r="N57" s="9"/>
       <c r="O57" s="7"/>
     </row>
-    <row r="58" spans="1:15" ht="26.75" customHeight="1">
+    <row r="58" spans="1:15" ht="26.85" customHeight="1">
       <c r="A58" s="7">
         <v>57</v>
       </c>
@@ -5964,7 +5982,7 @@
       <c r="N58" s="9"/>
       <c r="O58" s="7"/>
     </row>
-    <row r="59" spans="1:15" ht="26.75" customHeight="1">
+    <row r="59" spans="1:15" ht="26.85" customHeight="1">
       <c r="A59" s="7">
         <v>58</v>
       </c>
@@ -5978,10 +5996,10 @@
         <v>305</v>
       </c>
       <c r="E59" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>810</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>811</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>306</v>
@@ -6003,7 +6021,7 @@
       <c r="N59" s="9"/>
       <c r="O59" s="7"/>
     </row>
-    <row r="60" spans="1:15" ht="26.75" customHeight="1">
+    <row r="60" spans="1:15" ht="26.85" customHeight="1">
       <c r="A60" s="7">
         <v>59</v>
       </c>
@@ -6017,7 +6035,7 @@
         <v>307</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>304</v>
@@ -6042,7 +6060,7 @@
       <c r="N60" s="9"/>
       <c r="O60" s="7"/>
     </row>
-    <row r="61" spans="1:15" ht="47" customHeight="1">
+    <row r="61" spans="1:15" ht="47.1" customHeight="1">
       <c r="A61" s="7">
         <v>60</v>
       </c>
@@ -6056,7 +6074,7 @@
         <v>310</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>304</v>
@@ -6081,7 +6099,7 @@
       <c r="N61" s="9"/>
       <c r="O61" s="7"/>
     </row>
-    <row r="62" spans="1:15" ht="47" customHeight="1">
+    <row r="62" spans="1:15" ht="47.1" customHeight="1">
       <c r="A62" s="7">
         <v>61</v>
       </c>
@@ -6120,7 +6138,7 @@
       <c r="N62" s="9"/>
       <c r="O62" s="7"/>
     </row>
-    <row r="63" spans="1:15" ht="26.75" customHeight="1">
+    <row r="63" spans="1:15" ht="26.85" customHeight="1">
       <c r="A63" s="7">
         <v>62</v>
       </c>
@@ -6159,7 +6177,7 @@
       <c r="N63" s="9"/>
       <c r="O63" s="7"/>
     </row>
-    <row r="64" spans="1:15" ht="47" customHeight="1">
+    <row r="64" spans="1:15" ht="47.1" customHeight="1">
       <c r="A64" s="7">
         <v>63</v>
       </c>
@@ -6198,7 +6216,7 @@
       <c r="N64" s="9"/>
       <c r="O64" s="7"/>
     </row>
-    <row r="65" spans="1:15" ht="26.75" customHeight="1">
+    <row r="65" spans="1:15" ht="26.85" customHeight="1">
       <c r="A65" s="7">
         <v>64</v>
       </c>
@@ -6237,7 +6255,7 @@
       <c r="N65" s="9"/>
       <c r="O65" s="7"/>
     </row>
-    <row r="66" spans="1:15" ht="26.75" customHeight="1">
+    <row r="66" spans="1:15" ht="26.85" customHeight="1">
       <c r="A66" s="7">
         <v>65</v>
       </c>
@@ -6248,16 +6266,16 @@
         <v>273</v>
       </c>
       <c r="D66" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>814</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>815</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>330</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H66" s="8" t="s">
         <v>59</v>
@@ -6276,7 +6294,7 @@
       <c r="N66" s="9"/>
       <c r="O66" s="7"/>
     </row>
-    <row r="67" spans="1:15" ht="26.75" customHeight="1">
+    <row r="67" spans="1:15" ht="26.85" customHeight="1">
       <c r="A67" s="7">
         <v>66</v>
       </c>
@@ -6315,7 +6333,7 @@
       <c r="N67" s="9"/>
       <c r="O67" s="7"/>
     </row>
-    <row r="68" spans="1:15" ht="26.75" customHeight="1">
+    <row r="68" spans="1:15" ht="26.85" customHeight="1">
       <c r="A68" s="7">
         <v>67</v>
       </c>
@@ -6354,7 +6372,7 @@
       <c r="N68" s="9"/>
       <c r="O68" s="7"/>
     </row>
-    <row r="69" spans="1:15" ht="47" customHeight="1">
+    <row r="69" spans="1:15" ht="47.1" customHeight="1">
       <c r="A69" s="7">
         <v>68</v>
       </c>
@@ -6393,7 +6411,7 @@
       <c r="N69" s="9"/>
       <c r="O69" s="7"/>
     </row>
-    <row r="70" spans="1:15" ht="47" customHeight="1">
+    <row r="70" spans="1:15" ht="47.1" customHeight="1">
       <c r="A70" s="7">
         <v>69</v>
       </c>
@@ -6432,7 +6450,7 @@
       <c r="N70" s="9"/>
       <c r="O70" s="7"/>
     </row>
-    <row r="71" spans="1:15" ht="70.25" customHeight="1">
+    <row r="71" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A71" s="7">
         <v>70</v>
       </c>
@@ -6471,7 +6489,7 @@
       <c r="N71" s="9"/>
       <c r="O71" s="7"/>
     </row>
-    <row r="72" spans="1:15" ht="26.75" customHeight="1">
+    <row r="72" spans="1:15" ht="26.85" customHeight="1">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -6510,7 +6528,7 @@
       <c r="N72" s="9"/>
       <c r="O72" s="7"/>
     </row>
-    <row r="73" spans="1:15" ht="26.75" customHeight="1">
+    <row r="73" spans="1:15" ht="26.85" customHeight="1">
       <c r="A73" s="7">
         <v>72</v>
       </c>
@@ -6549,7 +6567,7 @@
       <c r="N73" s="9"/>
       <c r="O73" s="7"/>
     </row>
-    <row r="74" spans="1:15" ht="47" customHeight="1">
+    <row r="74" spans="1:15" ht="47.1" customHeight="1">
       <c r="A74" s="7">
         <v>73</v>
       </c>
@@ -6563,7 +6581,7 @@
         <v>362</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>363</v>
@@ -6588,7 +6606,7 @@
       <c r="N74" s="9"/>
       <c r="O74" s="7"/>
     </row>
-    <row r="75" spans="1:15" ht="70.25" customHeight="1">
+    <row r="75" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A75" s="7">
         <v>74</v>
       </c>
@@ -6602,7 +6620,7 @@
         <v>366</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>367</v>
@@ -6627,7 +6645,7 @@
       <c r="N75" s="9"/>
       <c r="O75" s="7"/>
     </row>
-    <row r="76" spans="1:15" ht="70.25" customHeight="1">
+    <row r="76" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A76" s="7">
         <v>75</v>
       </c>
@@ -6666,7 +6684,7 @@
       <c r="N76" s="9"/>
       <c r="O76" s="7"/>
     </row>
-    <row r="77" spans="1:15" ht="26.75" customHeight="1">
+    <row r="77" spans="1:15" ht="26.85" customHeight="1">
       <c r="A77" s="7">
         <v>76</v>
       </c>
@@ -6705,7 +6723,7 @@
       <c r="N77" s="9"/>
       <c r="O77" s="7"/>
     </row>
-    <row r="78" spans="1:15" ht="70.25" customHeight="1">
+    <row r="78" spans="1:15" ht="70.349999999999994" customHeight="1">
       <c r="A78" s="7">
         <v>77</v>
       </c>
@@ -6719,7 +6737,7 @@
         <v>379</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>380</v>
@@ -6744,7 +6762,7 @@
       <c r="N78" s="9"/>
       <c r="O78" s="7"/>
     </row>
-    <row r="79" spans="1:15" ht="47" customHeight="1">
+    <row r="79" spans="1:15" ht="47.1" customHeight="1">
       <c r="A79" s="7">
         <v>78</v>
       </c>
@@ -6758,7 +6776,7 @@
         <v>383</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>384</v>
@@ -6783,7 +6801,7 @@
       <c r="N79" s="9"/>
       <c r="O79" s="7"/>
     </row>
-    <row r="80" spans="1:15" ht="26.75" customHeight="1">
+    <row r="80" spans="1:15" ht="26.85" customHeight="1">
       <c r="A80" s="7">
         <v>79</v>
       </c>
@@ -6822,7 +6840,7 @@
       <c r="N80" s="9"/>
       <c r="O80" s="7"/>
     </row>
-    <row r="81" spans="1:15" ht="47" customHeight="1">
+    <row r="81" spans="1:15" ht="47.1" customHeight="1">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -6861,7 +6879,7 @@
       <c r="N81" s="9"/>
       <c r="O81" s="7"/>
     </row>
-    <row r="82" spans="1:15" ht="47" customHeight="1">
+    <row r="82" spans="1:15" ht="47.1" customHeight="1">
       <c r="A82" s="7">
         <v>81</v>
       </c>
@@ -6900,7 +6918,7 @@
       <c r="N82" s="9"/>
       <c r="O82" s="7"/>
     </row>
-    <row r="83" spans="1:15" ht="47" customHeight="1">
+    <row r="83" spans="1:15" ht="47.1" customHeight="1">
       <c r="A83" s="7">
         <v>82</v>
       </c>
@@ -6939,7 +6957,7 @@
       <c r="N83" s="9"/>
       <c r="O83" s="7"/>
     </row>
-    <row r="84" spans="1:15" ht="26.75" customHeight="1">
+    <row r="84" spans="1:15" ht="26.85" customHeight="1">
       <c r="A84" s="7">
         <v>83</v>
       </c>
@@ -6978,7 +6996,7 @@
       <c r="N84" s="9"/>
       <c r="O84" s="7"/>
     </row>
-    <row r="85" spans="1:15" ht="26.75" customHeight="1">
+    <row r="85" spans="1:15" ht="26.85" customHeight="1">
       <c r="A85" s="7">
         <v>84</v>
       </c>
@@ -7017,7 +7035,7 @@
       <c r="N85" s="9"/>
       <c r="O85" s="7"/>
     </row>
-    <row r="86" spans="1:15" ht="47" customHeight="1">
+    <row r="86" spans="1:15" ht="47.1" customHeight="1">
       <c r="A86" s="7">
         <v>85</v>
       </c>
@@ -7056,7 +7074,7 @@
       <c r="N86" s="9"/>
       <c r="O86" s="7"/>
     </row>
-    <row r="87" spans="1:15" ht="47" customHeight="1">
+    <row r="87" spans="1:15" ht="47.1" customHeight="1">
       <c r="A87" s="7">
         <v>86</v>
       </c>
@@ -7095,7 +7113,7 @@
       <c r="N87" s="9"/>
       <c r="O87" s="7"/>
     </row>
-    <row r="88" spans="1:15" ht="47" customHeight="1">
+    <row r="88" spans="1:15" ht="47.1" customHeight="1">
       <c r="A88" s="7">
         <v>87</v>
       </c>
@@ -7134,7 +7152,7 @@
       <c r="N88" s="9"/>
       <c r="O88" s="7"/>
     </row>
-    <row r="89" spans="1:15" ht="47" customHeight="1">
+    <row r="89" spans="1:15" ht="47.1" customHeight="1">
       <c r="A89" s="7">
         <v>88</v>
       </c>
@@ -7148,7 +7166,7 @@
         <v>425</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>426</v>
@@ -7169,13 +7187,13 @@
         <v>61</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M89" s="9"/>
       <c r="N89" s="9"/>
       <c r="O89" s="7"/>
     </row>
-    <row r="90" spans="1:15" ht="26.75" customHeight="1">
+    <row r="90" spans="1:15" ht="26.85" customHeight="1">
       <c r="A90" s="7">
         <v>89</v>
       </c>
@@ -7210,13 +7228,13 @@
         <v>61</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="M90" s="9"/>
       <c r="N90" s="9"/>
       <c r="O90" s="7"/>
     </row>
-    <row r="91" spans="1:15" ht="47" customHeight="1">
+    <row r="91" spans="1:15" ht="47.1" customHeight="1">
       <c r="A91" s="7">
         <v>90</v>
       </c>
@@ -7251,13 +7269,13 @@
         <v>61</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M91" s="9"/>
       <c r="N91" s="9"/>
       <c r="O91" s="7"/>
     </row>
-    <row r="92" spans="1:15" ht="47" customHeight="1">
+    <row r="92" spans="1:15" ht="47.1" customHeight="1">
       <c r="A92" s="7">
         <v>91</v>
       </c>
@@ -7292,13 +7310,13 @@
         <v>61</v>
       </c>
       <c r="L92" s="9" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M92" s="9"/>
       <c r="N92" s="9"/>
       <c r="O92" s="7"/>
     </row>
-    <row r="93" spans="1:15" ht="47" customHeight="1">
+    <row r="93" spans="1:15" ht="47.1" customHeight="1">
       <c r="A93" s="7">
         <v>92</v>
       </c>
@@ -7333,13 +7351,13 @@
         <v>61</v>
       </c>
       <c r="L93" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="M93" s="9"/>
       <c r="N93" s="9"/>
       <c r="O93" s="7"/>
     </row>
-    <row r="94" spans="1:15" ht="47" customHeight="1">
+    <row r="94" spans="1:15" ht="47.1" customHeight="1">
       <c r="A94" s="7">
         <v>93</v>
       </c>
@@ -7378,7 +7396,7 @@
       <c r="N94" s="9"/>
       <c r="O94" s="7"/>
     </row>
-    <row r="95" spans="1:15" ht="47" customHeight="1">
+    <row r="95" spans="1:15" ht="47.1" customHeight="1">
       <c r="A95" s="7">
         <v>94</v>
       </c>
@@ -7413,13 +7431,13 @@
         <v>22</v>
       </c>
       <c r="L95" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M95" s="9"/>
       <c r="N95" s="9"/>
       <c r="O95" s="7"/>
     </row>
-    <row r="96" spans="1:15" ht="47" customHeight="1">
+    <row r="96" spans="1:15" ht="47.1" customHeight="1">
       <c r="A96" s="7">
         <v>95</v>
       </c>
@@ -7454,13 +7472,13 @@
         <v>61</v>
       </c>
       <c r="L96" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M96" s="9"/>
       <c r="N96" s="9"/>
       <c r="O96" s="7"/>
     </row>
-    <row r="97" spans="1:15" ht="47" customHeight="1">
+    <row r="97" spans="1:15" ht="47.1" customHeight="1">
       <c r="A97" s="7">
         <v>96</v>
       </c>
@@ -7495,13 +7513,13 @@
         <v>61</v>
       </c>
       <c r="L97" s="9" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M97" s="9"/>
       <c r="N97" s="9"/>
       <c r="O97" s="7"/>
     </row>
-    <row r="98" spans="1:15" ht="47" customHeight="1">
+    <row r="98" spans="1:15" ht="47.1" customHeight="1">
       <c r="A98" s="7">
         <v>97</v>
       </c>
@@ -7536,13 +7554,13 @@
         <v>61</v>
       </c>
       <c r="L98" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M98" s="9"/>
       <c r="N98" s="9"/>
       <c r="O98" s="7"/>
     </row>
-    <row r="99" spans="1:15" ht="26.75" customHeight="1">
+    <row r="99" spans="1:15" ht="26.85" customHeight="1">
       <c r="A99" s="7">
         <v>98</v>
       </c>
@@ -7577,13 +7595,13 @@
         <v>61</v>
       </c>
       <c r="L99" s="9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M99" s="9"/>
       <c r="N99" s="9"/>
       <c r="O99" s="7"/>
     </row>
-    <row r="100" spans="1:15" ht="26.75" customHeight="1">
+    <row r="100" spans="1:15" ht="26.85" customHeight="1">
       <c r="A100" s="7">
         <v>99</v>
       </c>
@@ -7618,13 +7636,13 @@
         <v>61</v>
       </c>
       <c r="L100" s="9" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M100" s="9"/>
       <c r="N100" s="9"/>
       <c r="O100" s="7"/>
     </row>
-    <row r="101" spans="1:15" ht="26.75" customHeight="1">
+    <row r="101" spans="1:15" ht="26.85" customHeight="1">
       <c r="A101" s="7">
         <v>100</v>
       </c>
@@ -7659,13 +7677,13 @@
         <v>61</v>
       </c>
       <c r="L101" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M101" s="9"/>
       <c r="N101" s="9"/>
       <c r="O101" s="7"/>
     </row>
-    <row r="102" spans="1:15" ht="26.75" customHeight="1">
+    <row r="102" spans="1:15" ht="26.85" customHeight="1">
       <c r="A102" s="7">
         <v>101</v>
       </c>
@@ -7700,13 +7718,13 @@
         <v>61</v>
       </c>
       <c r="L102" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M102" s="9"/>
       <c r="N102" s="9"/>
       <c r="O102" s="7"/>
     </row>
-    <row r="103" spans="1:15" ht="26.75" customHeight="1">
+    <row r="103" spans="1:15" ht="26.85" customHeight="1">
       <c r="A103" s="7">
         <v>102</v>
       </c>
@@ -7741,13 +7759,13 @@
         <v>22</v>
       </c>
       <c r="L103" s="9" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="M103" s="9"/>
       <c r="N103" s="9"/>
       <c r="O103" s="7"/>
     </row>
-    <row r="104" spans="1:15" ht="26.75" customHeight="1">
+    <row r="104" spans="1:15" ht="26.85" customHeight="1">
       <c r="A104" s="7">
         <v>103</v>
       </c>
@@ -7782,13 +7800,13 @@
         <v>61</v>
       </c>
       <c r="L104" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="M104" s="9"/>
       <c r="N104" s="9"/>
       <c r="O104" s="7"/>
     </row>
-    <row r="105" spans="1:15" ht="26.75" customHeight="1">
+    <row r="105" spans="1:15" ht="26.85" customHeight="1">
       <c r="A105" s="7">
         <v>104</v>
       </c>
@@ -7823,13 +7841,13 @@
         <v>61</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="M105" s="9"/>
       <c r="N105" s="9"/>
       <c r="O105" s="7"/>
     </row>
-    <row r="106" spans="1:15" ht="26.75" customHeight="1">
+    <row r="106" spans="1:15" ht="26.85" customHeight="1">
       <c r="A106" s="7">
         <v>105</v>
       </c>
@@ -7864,13 +7882,13 @@
         <v>61</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="M106" s="9"/>
       <c r="N106" s="9"/>
       <c r="O106" s="7"/>
     </row>
-    <row r="107" spans="1:15" ht="26.75" customHeight="1">
+    <row r="107" spans="1:15" ht="26.85" customHeight="1">
       <c r="A107" s="7">
         <v>106</v>
       </c>
@@ -7905,13 +7923,13 @@
         <v>61</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="M107" s="9"/>
       <c r="N107" s="9"/>
       <c r="O107" s="7"/>
     </row>
-    <row r="108" spans="1:15" ht="47" customHeight="1">
+    <row r="108" spans="1:15" ht="47.1" customHeight="1">
       <c r="A108" s="7">
         <v>107</v>
       </c>
@@ -7946,13 +7964,13 @@
         <v>61</v>
       </c>
       <c r="L108" s="9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M108" s="9"/>
       <c r="N108" s="9"/>
       <c r="O108" s="7"/>
     </row>
-    <row r="109" spans="1:15" ht="26.75" customHeight="1">
+    <row r="109" spans="1:15" ht="26.85" customHeight="1">
       <c r="A109" s="7">
         <v>108</v>
       </c>
@@ -7987,13 +8005,13 @@
         <v>61</v>
       </c>
       <c r="L109" s="9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="M109" s="9"/>
       <c r="N109" s="9"/>
       <c r="O109" s="7"/>
     </row>
-    <row r="110" spans="1:15" ht="26.75" customHeight="1">
+    <row r="110" spans="1:15" ht="26.85" customHeight="1">
       <c r="A110" s="7">
         <v>109</v>
       </c>
@@ -8028,13 +8046,13 @@
         <v>61</v>
       </c>
       <c r="L110" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M110" s="9"/>
       <c r="N110" s="9"/>
       <c r="O110" s="7"/>
     </row>
-    <row r="111" spans="1:15" ht="26.75" customHeight="1">
+    <row r="111" spans="1:15" ht="26.85" customHeight="1">
       <c r="A111" s="7">
         <v>110</v>
       </c>
@@ -8063,7 +8081,7 @@
         <v>2</v>
       </c>
       <c r="J111" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K111" s="8" t="s">
         <v>192</v>
@@ -8073,7 +8091,7 @@
       <c r="N111" s="9"/>
       <c r="O111" s="7"/>
     </row>
-    <row r="112" spans="1:15" ht="26.75" customHeight="1">
+    <row r="112" spans="1:15" ht="26.85" customHeight="1">
       <c r="A112" s="7">
         <v>111</v>
       </c>
@@ -8102,7 +8120,7 @@
         <v>2</v>
       </c>
       <c r="J112" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K112" s="8" t="s">
         <v>192</v>
@@ -8112,7 +8130,7 @@
       <c r="N112" s="9"/>
       <c r="O112" s="7"/>
     </row>
-    <row r="113" spans="1:15" ht="47" customHeight="1">
+    <row r="113" spans="1:15" ht="47.1" customHeight="1">
       <c r="A113" s="7">
         <v>112</v>
       </c>
@@ -8123,17 +8141,17 @@
         <v>523</v>
       </c>
       <c r="D113" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="E113" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="F113" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="G113" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="G113" s="7" t="s">
-        <v>527</v>
-      </c>
       <c r="H113" s="8" t="s">
         <v>59</v>
       </c>
@@ -8141,7 +8159,7 @@
         <v>2</v>
       </c>
       <c r="J113" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K113" s="8" t="s">
         <v>192</v>
@@ -8151,7 +8169,7 @@
       <c r="N113" s="9"/>
       <c r="O113" s="7"/>
     </row>
-    <row r="114" spans="1:15" ht="26.75" customHeight="1">
+    <row r="114" spans="1:15" ht="26.85" customHeight="1">
       <c r="A114" s="7">
         <v>113</v>
       </c>
@@ -8162,17 +8180,17 @@
         <v>523</v>
       </c>
       <c r="D114" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="E114" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="F114" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="G114" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>531</v>
-      </c>
       <c r="H114" s="8" t="s">
         <v>59</v>
       </c>
@@ -8180,7 +8198,7 @@
         <v>2</v>
       </c>
       <c r="J114" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K114" s="8" t="s">
         <v>192</v>
@@ -8190,7 +8208,7 @@
       <c r="N114" s="9"/>
       <c r="O114" s="7"/>
     </row>
-    <row r="115" spans="1:15" ht="26.75" customHeight="1">
+    <row r="115" spans="1:15" ht="26.85" customHeight="1">
       <c r="A115" s="7">
         <v>114</v>
       </c>
@@ -8201,17 +8219,17 @@
         <v>523</v>
       </c>
       <c r="D115" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="F115" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="G115" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="G115" s="7" t="s">
-        <v>535</v>
-      </c>
       <c r="H115" s="8" t="s">
         <v>59</v>
       </c>
@@ -8219,7 +8237,7 @@
         <v>2</v>
       </c>
       <c r="J115" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K115" s="8" t="s">
         <v>192</v>
@@ -8229,7 +8247,7 @@
       <c r="N115" s="9"/>
       <c r="O115" s="7"/>
     </row>
-    <row r="116" spans="1:15" ht="26.75" customHeight="1">
+    <row r="116" spans="1:15" ht="26.85" customHeight="1">
       <c r="A116" s="7">
         <v>115</v>
       </c>
@@ -8240,17 +8258,17 @@
         <v>523</v>
       </c>
       <c r="D116" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="E116" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="F116" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="G116" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="G116" s="7" t="s">
-        <v>539</v>
-      </c>
       <c r="H116" s="8" t="s">
         <v>59</v>
       </c>
@@ -8258,7 +8276,7 @@
         <v>2</v>
       </c>
       <c r="J116" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K116" s="8" t="s">
         <v>192</v>
@@ -8268,7 +8286,7 @@
       <c r="N116" s="9"/>
       <c r="O116" s="7"/>
     </row>
-    <row r="117" spans="1:15" ht="26.75" customHeight="1">
+    <row r="117" spans="1:15" ht="26.85" customHeight="1">
       <c r="A117" s="7">
         <v>116</v>
       </c>
@@ -8276,19 +8294,19 @@
         <v>36</v>
       </c>
       <c r="C117" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="D117" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="E117" s="7" t="s">
         <v>541</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>542</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>417</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H117" s="8" t="s">
         <v>59</v>
@@ -8297,7 +8315,7 @@
         <v>2</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K117" s="8" t="s">
         <v>192</v>
@@ -8307,7 +8325,7 @@
       <c r="N117" s="9"/>
       <c r="O117" s="7"/>
     </row>
-    <row r="118" spans="1:15" ht="26.75" customHeight="1">
+    <row r="118" spans="1:15" ht="26.85" customHeight="1">
       <c r="A118" s="7">
         <v>117</v>
       </c>
@@ -8315,19 +8333,19 @@
         <v>36</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D118" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>544</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>545</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>431</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H118" s="8" t="s">
         <v>59</v>
@@ -8336,7 +8354,7 @@
         <v>2</v>
       </c>
       <c r="J118" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K118" s="8" t="s">
         <v>192</v>
@@ -8346,7 +8364,7 @@
       <c r="N118" s="9"/>
       <c r="O118" s="7"/>
     </row>
-    <row r="119" spans="1:15" ht="26.75" customHeight="1">
+    <row r="119" spans="1:15" ht="26.85" customHeight="1">
       <c r="A119" s="7">
         <v>118</v>
       </c>
@@ -8354,20 +8372,20 @@
         <v>36</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D119" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="F119" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="F119" s="7" t="s">
+      <c r="G119" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="G119" s="7" t="s">
-        <v>550</v>
-      </c>
       <c r="H119" s="8" t="s">
         <v>59</v>
       </c>
@@ -8375,7 +8393,7 @@
         <v>2</v>
       </c>
       <c r="J119" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K119" s="8" t="s">
         <v>192</v>
@@ -8385,7 +8403,7 @@
       <c r="N119" s="9"/>
       <c r="O119" s="7"/>
     </row>
-    <row r="120" spans="1:15" ht="26.75" customHeight="1">
+    <row r="120" spans="1:15" ht="26.85" customHeight="1">
       <c r="A120" s="7">
         <v>119</v>
       </c>
@@ -8393,20 +8411,20 @@
         <v>36</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D120" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="E120" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="F120" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="F120" s="7" t="s">
+      <c r="G120" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="G120" s="7" t="s">
-        <v>554</v>
-      </c>
       <c r="H120" s="8" t="s">
         <v>59</v>
       </c>
@@ -8414,7 +8432,7 @@
         <v>2</v>
       </c>
       <c r="J120" s="8" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="K120" s="8" t="s">
         <v>192</v>
@@ -8424,7 +8442,7 @@
       <c r="N120" s="9"/>
       <c r="O120" s="7"/>
     </row>
-    <row r="121" spans="1:15" ht="26.75" customHeight="1">
+    <row r="121" spans="1:15" ht="26.85" customHeight="1">
       <c r="A121" s="7">
         <v>120</v>
       </c>
@@ -8432,19 +8450,19 @@
         <v>36</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D121" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="E121" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="E121" s="7" t="s">
+      <c r="F121" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G121" s="7" t="s">
         <v>556</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="G121" s="7" t="s">
-        <v>557</v>
       </c>
       <c r="H121" s="8" t="s">
         <v>59</v>
@@ -8463,7 +8481,7 @@
       <c r="N121" s="9"/>
       <c r="O121" s="7"/>
     </row>
-    <row r="122" spans="1:15" ht="26.75" customHeight="1">
+    <row r="122" spans="1:15" ht="26.85" customHeight="1">
       <c r="A122" s="7">
         <v>121</v>
       </c>
@@ -8471,19 +8489,19 @@
         <v>36</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D122" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E122" s="7" t="s">
         <v>558</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>559</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>426</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H122" s="8" t="s">
         <v>59</v>
@@ -8502,7 +8520,7 @@
       <c r="N122" s="9"/>
       <c r="O122" s="7"/>
     </row>
-    <row r="123" spans="1:15" ht="26.75" customHeight="1">
+    <row r="123" spans="1:15" ht="26.85" customHeight="1">
       <c r="A123" s="7">
         <v>122</v>
       </c>
@@ -8510,19 +8528,19 @@
         <v>36</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="D123" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="E123" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="F123" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="F123" s="7" t="s">
+      <c r="G123" s="7" t="s">
         <v>564</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>565</v>
       </c>
       <c r="H123" s="8" t="s">
         <v>59</v>
@@ -8541,7 +8559,7 @@
       <c r="N123" s="9"/>
       <c r="O123" s="7"/>
     </row>
-    <row r="124" spans="1:15" ht="26.75" customHeight="1">
+    <row r="124" spans="1:15" ht="26.85" customHeight="1">
       <c r="A124" s="7">
         <v>123</v>
       </c>
@@ -8549,19 +8567,19 @@
         <v>36</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D124" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="E124" s="7" t="s">
         <v>566</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>567</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>431</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H124" s="8" t="s">
         <v>59</v>
@@ -8580,7 +8598,7 @@
       <c r="N124" s="9"/>
       <c r="O124" s="7"/>
     </row>
-    <row r="125" spans="1:15" ht="26.75" customHeight="1">
+    <row r="125" spans="1:15" ht="26.85" customHeight="1">
       <c r="A125" s="7">
         <v>124</v>
       </c>
@@ -8588,19 +8606,19 @@
         <v>36</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D125" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="E125" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="F125" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="G125" s="7" t="s">
         <v>570</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>571</v>
       </c>
       <c r="H125" s="8" t="s">
         <v>59</v>
@@ -8619,7 +8637,7 @@
       <c r="N125" s="9"/>
       <c r="O125" s="7"/>
     </row>
-    <row r="126" spans="1:15" ht="26.75" customHeight="1">
+    <row r="126" spans="1:15" ht="26.85" customHeight="1">
       <c r="A126" s="7">
         <v>125</v>
       </c>
@@ -8627,19 +8645,19 @@
         <v>36</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D126" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="E126" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>573</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>426</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>59</v>
@@ -8658,7 +8676,7 @@
       <c r="N126" s="9"/>
       <c r="O126" s="7"/>
     </row>
-    <row r="127" spans="1:15" ht="26.75" customHeight="1">
+    <row r="127" spans="1:15" ht="26.85" customHeight="1">
       <c r="A127" s="7">
         <v>126</v>
       </c>
@@ -8666,19 +8684,19 @@
         <v>36</v>
       </c>
       <c r="C127" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D127" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="E127" s="7" t="s">
         <v>576</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>577</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>417</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H127" s="8" t="s">
         <v>59</v>
@@ -8697,7 +8715,7 @@
       <c r="N127" s="9"/>
       <c r="O127" s="7"/>
     </row>
-    <row r="128" spans="1:15" ht="26.75" customHeight="1">
+    <row r="128" spans="1:15" ht="26.85" customHeight="1">
       <c r="A128" s="7">
         <v>127</v>
       </c>
@@ -8705,19 +8723,19 @@
         <v>36</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>431</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H128" s="8" t="s">
         <v>59</v>
@@ -8736,7 +8754,7 @@
       <c r="N128" s="9"/>
       <c r="O128" s="7"/>
     </row>
-    <row r="129" spans="1:15" ht="26.75" customHeight="1">
+    <row r="129" spans="1:15" ht="26.85" customHeight="1">
       <c r="A129" s="7">
         <v>128</v>
       </c>
@@ -8744,19 +8762,19 @@
         <v>36</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D129" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="E129" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="F129" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="F129" s="7" t="s">
+      <c r="G129" s="7" t="s">
         <v>582</v>
-      </c>
-      <c r="G129" s="7" t="s">
-        <v>583</v>
       </c>
       <c r="H129" s="8" t="s">
         <v>59</v>
@@ -8775,7 +8793,7 @@
       <c r="N129" s="9"/>
       <c r="O129" s="7"/>
     </row>
-    <row r="130" spans="1:15" ht="26.75" customHeight="1">
+    <row r="130" spans="1:15" ht="26.85" customHeight="1">
       <c r="A130" s="7">
         <v>129</v>
       </c>
@@ -8783,19 +8801,19 @@
         <v>36</v>
       </c>
       <c r="C130" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="D130" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="E130" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="F130" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="E130" s="7" t="s">
-        <v>844</v>
-      </c>
-      <c r="F130" s="7" t="s">
+      <c r="G130" s="7" t="s">
         <v>586</v>
-      </c>
-      <c r="G130" s="7" t="s">
-        <v>587</v>
       </c>
       <c r="H130" s="8" t="s">
         <v>59</v>
@@ -8814,7 +8832,7 @@
       <c r="N130" s="9"/>
       <c r="O130" s="7"/>
     </row>
-    <row r="131" spans="1:15" ht="26.75" customHeight="1">
+    <row r="131" spans="1:15" ht="26.85" customHeight="1">
       <c r="A131" s="7">
         <v>130</v>
       </c>
@@ -8822,19 +8840,19 @@
         <v>36</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D131" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="E131" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="F131" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="G131" s="7" t="s">
         <v>590</v>
-      </c>
-      <c r="G131" s="7" t="s">
-        <v>591</v>
       </c>
       <c r="H131" s="8" t="s">
         <v>59</v>
@@ -8853,7 +8871,7 @@
       <c r="N131" s="9"/>
       <c r="O131" s="7"/>
     </row>
-    <row r="132" spans="1:15" ht="26.75" customHeight="1">
+    <row r="132" spans="1:15" ht="26.85" customHeight="1">
       <c r="A132" s="7">
         <v>131</v>
       </c>
@@ -8861,19 +8879,19 @@
         <v>36</v>
       </c>
       <c r="C132" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D132" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="E132" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="F132" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="G132" s="7" t="s">
         <v>595</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>596</v>
       </c>
       <c r="H132" s="8" t="s">
         <v>59</v>
@@ -8892,7 +8910,7 @@
       <c r="N132" s="9"/>
       <c r="O132" s="7"/>
     </row>
-    <row r="133" spans="1:15" ht="26.75" customHeight="1">
+    <row r="133" spans="1:15" ht="26.85" customHeight="1">
       <c r="A133" s="7">
         <v>132</v>
       </c>
@@ -8900,13 +8918,13 @@
         <v>37</v>
       </c>
       <c r="C133" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="E133" s="7" t="s">
         <v>598</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>599</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>417</v>
@@ -8931,7 +8949,7 @@
       <c r="N133" s="9"/>
       <c r="O133" s="7"/>
     </row>
-    <row r="134" spans="1:15" ht="26.75" customHeight="1">
+    <row r="134" spans="1:15" ht="26.85" customHeight="1">
       <c r="A134" s="7">
         <v>133</v>
       </c>
@@ -8939,13 +8957,13 @@
         <v>37</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D134" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="E134" s="7" t="s">
         <v>600</v>
-      </c>
-      <c r="E134" s="7" t="s">
-        <v>601</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>431</v>
@@ -8970,7 +8988,7 @@
       <c r="N134" s="9"/>
       <c r="O134" s="7"/>
     </row>
-    <row r="135" spans="1:15" ht="47" customHeight="1">
+    <row r="135" spans="1:15" ht="47.1" customHeight="1">
       <c r="A135" s="7">
         <v>134</v>
       </c>
@@ -8978,16 +8996,16 @@
         <v>37</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D135" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E135" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="E135" s="7" t="s">
-        <v>603</v>
-      </c>
       <c r="F135" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>287</v>
@@ -9009,7 +9027,7 @@
       <c r="N135" s="9"/>
       <c r="O135" s="7"/>
     </row>
-    <row r="136" spans="1:15" ht="26.75" customHeight="1">
+    <row r="136" spans="1:15" ht="26.85" customHeight="1">
       <c r="A136" s="7">
         <v>135</v>
       </c>
@@ -9017,13 +9035,13 @@
         <v>37</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D136" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="E136" s="7" t="s">
         <v>604</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>605</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>426</v>
@@ -9048,7 +9066,7 @@
       <c r="N136" s="9"/>
       <c r="O136" s="7"/>
     </row>
-    <row r="137" spans="1:15" ht="26.75" customHeight="1">
+    <row r="137" spans="1:15" ht="26.85" customHeight="1">
       <c r="A137" s="7">
         <v>136</v>
       </c>
@@ -9056,19 +9074,19 @@
         <v>37</v>
       </c>
       <c r="C137" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D137" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="E137" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="F137" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="F137" s="7" t="s">
+      <c r="G137" s="7" t="s">
         <v>609</v>
-      </c>
-      <c r="G137" s="7" t="s">
-        <v>610</v>
       </c>
       <c r="H137" s="8" t="s">
         <v>59</v>
@@ -9087,7 +9105,7 @@
       <c r="N137" s="9"/>
       <c r="O137" s="7"/>
     </row>
-    <row r="138" spans="1:15" ht="26.75" customHeight="1">
+    <row r="138" spans="1:15" ht="26.85" customHeight="1">
       <c r="A138" s="7">
         <v>137</v>
       </c>
@@ -9095,19 +9113,19 @@
         <v>37</v>
       </c>
       <c r="C138" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D138" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="E138" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="F138" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="G138" s="7" t="s">
         <v>614</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>615</v>
       </c>
       <c r="H138" s="8" t="s">
         <v>59</v>
@@ -9126,7 +9144,7 @@
       <c r="N138" s="9"/>
       <c r="O138" s="7"/>
     </row>
-    <row r="139" spans="1:15" ht="26.75" customHeight="1">
+    <row r="139" spans="1:15" ht="26.85" customHeight="1">
       <c r="A139" s="7">
         <v>138</v>
       </c>
@@ -9134,19 +9152,19 @@
         <v>37</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D139" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="F139" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="G139" s="7" t="s">
         <v>618</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>619</v>
       </c>
       <c r="H139" s="8" t="s">
         <v>59</v>
@@ -9165,7 +9183,7 @@
       <c r="N139" s="9"/>
       <c r="O139" s="7"/>
     </row>
-    <row r="140" spans="1:15" ht="26.75" customHeight="1">
+    <row r="140" spans="1:15" ht="26.85" customHeight="1">
       <c r="A140" s="7">
         <v>139</v>
       </c>
@@ -9173,19 +9191,19 @@
         <v>37</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D140" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="F140" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="G140" s="7" t="s">
         <v>622</v>
-      </c>
-      <c r="G140" s="7" t="s">
-        <v>623</v>
       </c>
       <c r="H140" s="8" t="s">
         <v>59</v>
@@ -9204,7 +9222,7 @@
       <c r="N140" s="9"/>
       <c r="O140" s="7"/>
     </row>
-    <row r="141" spans="1:15" ht="26.75" customHeight="1">
+    <row r="141" spans="1:15" ht="26.85" customHeight="1">
       <c r="A141" s="7">
         <v>140</v>
       </c>
@@ -9212,19 +9230,19 @@
         <v>37</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D141" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="E141" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="E141" s="7" t="s">
-        <v>625</v>
-      </c>
       <c r="F141" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="G141" s="7" t="s">
         <v>618</v>
-      </c>
-      <c r="G141" s="7" t="s">
-        <v>619</v>
       </c>
       <c r="H141" s="8" t="s">
         <v>59</v>
@@ -9243,7 +9261,7 @@
       <c r="N141" s="9"/>
       <c r="O141" s="7"/>
     </row>
-    <row r="142" spans="1:15" ht="47" customHeight="1">
+    <row r="142" spans="1:15" ht="47.1" customHeight="1">
       <c r="A142" s="7">
         <v>141</v>
       </c>
@@ -9251,19 +9269,19 @@
         <v>37</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D142" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="E142" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="F142" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="G142" s="7" t="s">
         <v>628</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>629</v>
       </c>
       <c r="H142" s="8" t="s">
         <v>59</v>
@@ -9282,7 +9300,7 @@
       <c r="N142" s="9"/>
       <c r="O142" s="7"/>
     </row>
-    <row r="143" spans="1:15" ht="26.75" customHeight="1">
+    <row r="143" spans="1:15" ht="26.85" customHeight="1">
       <c r="A143" s="7">
         <v>142</v>
       </c>
@@ -9290,19 +9308,19 @@
         <v>37</v>
       </c>
       <c r="C143" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="D143" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="E143" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="F143" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="G143" s="7" t="s">
         <v>633</v>
-      </c>
-      <c r="G143" s="7" t="s">
-        <v>634</v>
       </c>
       <c r="H143" s="8" t="s">
         <v>59</v>
@@ -9321,7 +9339,7 @@
       <c r="N143" s="9"/>
       <c r="O143" s="7"/>
     </row>
-    <row r="144" spans="1:15" ht="26.75" customHeight="1">
+    <row r="144" spans="1:15" ht="26.85" customHeight="1">
       <c r="A144" s="7">
         <v>143</v>
       </c>
@@ -9329,19 +9347,19 @@
         <v>37</v>
       </c>
       <c r="C144" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="D144" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="E144" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="F144" s="7" t="s">
         <v>637</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="G144" s="7" t="s">
         <v>638</v>
-      </c>
-      <c r="G144" s="7" t="s">
-        <v>639</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>59</v>
@@ -9360,7 +9378,7 @@
       <c r="N144" s="9"/>
       <c r="O144" s="7"/>
     </row>
-    <row r="145" spans="1:15" ht="26.75" customHeight="1">
+    <row r="145" spans="1:15" ht="26.85" customHeight="1">
       <c r="A145" s="7">
         <v>144</v>
       </c>
@@ -9368,19 +9386,19 @@
         <v>37</v>
       </c>
       <c r="C145" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="D145" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="E145" s="7" t="s">
         <v>641</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="F145" s="7" t="s">
         <v>642</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="G145" s="7" t="s">
         <v>643</v>
-      </c>
-      <c r="G145" s="7" t="s">
-        <v>644</v>
       </c>
       <c r="H145" s="8" t="s">
         <v>59</v>
@@ -9399,7 +9417,7 @@
       <c r="N145" s="9"/>
       <c r="O145" s="7"/>
     </row>
-    <row r="146" spans="1:15" ht="26.75" customHeight="1">
+    <row r="146" spans="1:15" ht="26.85" customHeight="1">
       <c r="A146" s="7">
         <v>145</v>
       </c>
@@ -9407,19 +9425,19 @@
         <v>37</v>
       </c>
       <c r="C146" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="D146" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="E146" s="7" t="s">
         <v>646</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="F146" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="G146" s="7" t="s">
         <v>648</v>
-      </c>
-      <c r="G146" s="7" t="s">
-        <v>649</v>
       </c>
       <c r="H146" s="8" t="s">
         <v>59</v>
@@ -9438,7 +9456,7 @@
       <c r="N146" s="9"/>
       <c r="O146" s="7"/>
     </row>
-    <row r="147" spans="1:15" ht="26.75" customHeight="1">
+    <row r="147" spans="1:15" ht="26.85" customHeight="1">
       <c r="A147" s="7">
         <v>146</v>
       </c>
@@ -9449,16 +9467,16 @@
         <v>115</v>
       </c>
       <c r="D147" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E147" s="7" t="s">
         <v>650</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="F147" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="F147" s="7" t="s">
+      <c r="G147" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="G147" s="7" t="s">
-        <v>653</v>
       </c>
       <c r="H147" s="8" t="s">
         <v>59</v>
@@ -9477,7 +9495,7 @@
       <c r="N147" s="9"/>
       <c r="O147" s="7"/>
     </row>
-    <row r="148" spans="1:15" ht="26.75" customHeight="1">
+    <row r="148" spans="1:15" ht="26.85" customHeight="1">
       <c r="A148" s="7">
         <v>147</v>
       </c>
@@ -9488,16 +9506,16 @@
         <v>115</v>
       </c>
       <c r="D148" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="E148" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="F148" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="F148" s="7" t="s">
+      <c r="G148" s="7" t="s">
         <v>656</v>
-      </c>
-      <c r="G148" s="7" t="s">
-        <v>657</v>
       </c>
       <c r="H148" s="8" t="s">
         <v>59</v>
@@ -9516,7 +9534,7 @@
       <c r="N148" s="9"/>
       <c r="O148" s="7"/>
     </row>
-    <row r="149" spans="1:15" ht="26.75" customHeight="1">
+    <row r="149" spans="1:15" ht="26.85" customHeight="1">
       <c r="A149" s="7">
         <v>148</v>
       </c>
@@ -9524,19 +9542,19 @@
         <v>38</v>
       </c>
       <c r="C149" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D149" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="E149" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="F149" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="G149" s="7" t="s">
         <v>661</v>
-      </c>
-      <c r="G149" s="7" t="s">
-        <v>662</v>
       </c>
       <c r="H149" s="8" t="s">
         <v>59</v>
@@ -9555,7 +9573,7 @@
       <c r="N149" s="9"/>
       <c r="O149" s="7"/>
     </row>
-    <row r="150" spans="1:15" ht="26.75" customHeight="1">
+    <row r="150" spans="1:15" ht="26.85" customHeight="1">
       <c r="A150" s="7">
         <v>149</v>
       </c>
@@ -9563,19 +9581,19 @@
         <v>38</v>
       </c>
       <c r="C150" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="D150" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="E150" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="F150" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="G150" s="7" t="s">
         <v>666</v>
-      </c>
-      <c r="G150" s="7" t="s">
-        <v>667</v>
       </c>
       <c r="H150" s="8" t="s">
         <v>59</v>
@@ -9594,7 +9612,7 @@
       <c r="N150" s="9"/>
       <c r="O150" s="7"/>
     </row>
-    <row r="151" spans="1:15" ht="47" customHeight="1">
+    <row r="151" spans="1:15" ht="47.1" customHeight="1">
       <c r="A151" s="7">
         <v>150</v>
       </c>
@@ -9602,19 +9620,19 @@
         <v>38</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D151" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="E151" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="F151" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="F151" s="7" t="s">
+      <c r="G151" s="7" t="s">
         <v>670</v>
-      </c>
-      <c r="G151" s="7" t="s">
-        <v>671</v>
       </c>
       <c r="H151" s="8" t="s">
         <v>59</v>
@@ -9633,7 +9651,7 @@
       <c r="N151" s="9"/>
       <c r="O151" s="7"/>
     </row>
-    <row r="152" spans="1:15" ht="47" customHeight="1">
+    <row r="152" spans="1:15" ht="47.1" customHeight="1">
       <c r="A152" s="7">
         <v>151</v>
       </c>
@@ -9641,19 +9659,19 @@
         <v>38</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D152" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="E152" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="F152" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="G152" s="7" t="s">
         <v>674</v>
-      </c>
-      <c r="G152" s="7" t="s">
-        <v>675</v>
       </c>
       <c r="H152" s="8" t="s">
         <v>59</v>
@@ -9672,7 +9690,7 @@
       <c r="N152" s="9"/>
       <c r="O152" s="7"/>
     </row>
-    <row r="153" spans="1:15" ht="26.75" customHeight="1">
+    <row r="153" spans="1:15" ht="26.85" customHeight="1">
       <c r="A153" s="7">
         <v>152</v>
       </c>
@@ -9680,19 +9698,19 @@
         <v>38</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D153" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="E153" s="7" t="s">
         <v>676</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="F153" s="7" t="s">
         <v>677</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="G153" s="7" t="s">
         <v>678</v>
-      </c>
-      <c r="G153" s="7" t="s">
-        <v>679</v>
       </c>
       <c r="H153" s="8" t="s">
         <v>59</v>
@@ -9711,7 +9729,7 @@
       <c r="N153" s="9"/>
       <c r="O153" s="7"/>
     </row>
-    <row r="154" spans="1:15" ht="26.75" customHeight="1">
+    <row r="154" spans="1:15" ht="26.85" customHeight="1">
       <c r="A154" s="7">
         <v>153</v>
       </c>
@@ -9719,19 +9737,19 @@
         <v>38</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D154" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="E154" s="7" t="s">
         <v>680</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="F154" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="G154" s="7" t="s">
         <v>682</v>
-      </c>
-      <c r="G154" s="7" t="s">
-        <v>683</v>
       </c>
       <c r="H154" s="8" t="s">
         <v>59</v>
@@ -9750,7 +9768,7 @@
       <c r="N154" s="9"/>
       <c r="O154" s="7"/>
     </row>
-    <row r="155" spans="1:15" ht="26.75" customHeight="1">
+    <row r="155" spans="1:15" ht="26.85" customHeight="1">
       <c r="A155" s="7">
         <v>154</v>
       </c>
@@ -9758,19 +9776,19 @@
         <v>38</v>
       </c>
       <c r="C155" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="D155" s="7" t="s">
         <v>684</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="E155" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="F155" s="7" t="s">
         <v>686</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="G155" s="7" t="s">
         <v>687</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>688</v>
       </c>
       <c r="H155" s="8" t="s">
         <v>59</v>
@@ -9789,7 +9807,7 @@
       <c r="N155" s="9"/>
       <c r="O155" s="7"/>
     </row>
-    <row r="156" spans="1:15" ht="26.75" customHeight="1">
+    <row r="156" spans="1:15" ht="26.85" customHeight="1">
       <c r="A156" s="7">
         <v>155</v>
       </c>
@@ -9797,19 +9815,19 @@
         <v>38</v>
       </c>
       <c r="C156" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="D156" s="7" t="s">
         <v>689</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="E156" s="7" t="s">
         <v>690</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="F156" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="G156" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="G156" s="7" t="s">
-        <v>693</v>
       </c>
       <c r="H156" s="8" t="s">
         <v>59</v>
@@ -9828,7 +9846,7 @@
       <c r="N156" s="9"/>
       <c r="O156" s="7"/>
     </row>
-    <row r="157" spans="1:15" ht="26.75" customHeight="1">
+    <row r="157" spans="1:15" ht="26.85" customHeight="1">
       <c r="A157" s="7">
         <v>156</v>
       </c>
@@ -9836,19 +9854,19 @@
         <v>38</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D157" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="E157" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="F157" s="7" t="s">
         <v>695</v>
       </c>
-      <c r="F157" s="7" t="s">
+      <c r="G157" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="G157" s="7" t="s">
-        <v>697</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>59</v>
@@ -9867,7 +9885,7 @@
       <c r="N157" s="9"/>
       <c r="O157" s="7"/>
     </row>
-    <row r="158" spans="1:15" ht="26.75" customHeight="1">
+    <row r="158" spans="1:15" ht="26.85" customHeight="1">
       <c r="A158" s="7">
         <v>157</v>
       </c>
@@ -9875,19 +9893,19 @@
         <v>38</v>
       </c>
       <c r="C158" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="D158" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="E158" s="7" t="s">
         <v>699</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="F158" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="F158" s="7" t="s">
+      <c r="G158" s="7" t="s">
         <v>701</v>
-      </c>
-      <c r="G158" s="7" t="s">
-        <v>702</v>
       </c>
       <c r="H158" s="8" t="s">
         <v>59</v>
@@ -9906,7 +9924,7 @@
       <c r="N158" s="9"/>
       <c r="O158" s="7"/>
     </row>
-    <row r="159" spans="1:15" ht="47" customHeight="1">
+    <row r="159" spans="1:15" ht="47.1" customHeight="1">
       <c r="A159" s="7">
         <v>158</v>
       </c>
@@ -9914,19 +9932,19 @@
         <v>39</v>
       </c>
       <c r="C159" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="D159" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="E159" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="F159" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="E159" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="F159" s="7" t="s">
+      <c r="G159" s="7" t="s">
         <v>705</v>
-      </c>
-      <c r="G159" s="7" t="s">
-        <v>706</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>59</v>
@@ -9945,7 +9963,7 @@
       <c r="N159" s="9"/>
       <c r="O159" s="7"/>
     </row>
-    <row r="160" spans="1:15" ht="26.75" customHeight="1">
+    <row r="160" spans="1:15" ht="26.85" customHeight="1">
       <c r="A160" s="7">
         <v>159</v>
       </c>
@@ -9953,19 +9971,19 @@
         <v>39</v>
       </c>
       <c r="C160" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="D160" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="E160" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="F160" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="F160" s="7" t="s">
+      <c r="G160" s="7" t="s">
         <v>710</v>
-      </c>
-      <c r="G160" s="7" t="s">
-        <v>711</v>
       </c>
       <c r="H160" s="8" t="s">
         <v>59</v>
@@ -9984,7 +10002,7 @@
       <c r="N160" s="9"/>
       <c r="O160" s="7"/>
     </row>
-    <row r="161" spans="1:15" ht="47" customHeight="1">
+    <row r="161" spans="1:15" ht="47.1" customHeight="1">
       <c r="A161" s="7">
         <v>160</v>
       </c>
@@ -9992,19 +10010,19 @@
         <v>39</v>
       </c>
       <c r="C161" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="D161" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="E161" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="F161" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="G161" s="7" t="s">
         <v>714</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>705</v>
-      </c>
-      <c r="G161" s="7" t="s">
-        <v>715</v>
       </c>
       <c r="H161" s="8" t="s">
         <v>59</v>
@@ -10023,7 +10041,7 @@
       <c r="N161" s="9"/>
       <c r="O161" s="7"/>
     </row>
-    <row r="162" spans="1:15" ht="47" customHeight="1">
+    <row r="162" spans="1:15" ht="47.1" customHeight="1">
       <c r="A162" s="7">
         <v>161</v>
       </c>
@@ -10034,16 +10052,16 @@
         <v>187</v>
       </c>
       <c r="D162" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="E162" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="F162" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="F162" s="7" t="s">
+      <c r="G162" s="7" t="s">
         <v>718</v>
-      </c>
-      <c r="G162" s="7" t="s">
-        <v>719</v>
       </c>
       <c r="H162" s="8" t="s">
         <v>59</v>
@@ -10062,7 +10080,7 @@
       <c r="N162" s="9"/>
       <c r="O162" s="7"/>
     </row>
-    <row r="163" spans="1:15" ht="26.75" customHeight="1">
+    <row r="163" spans="1:15" ht="26.85" customHeight="1">
       <c r="A163" s="7">
         <v>162</v>
       </c>
@@ -10073,16 +10091,16 @@
         <v>187</v>
       </c>
       <c r="D163" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="E163" s="7" t="s">
         <v>720</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="F163" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="F163" s="7" t="s">
+      <c r="G163" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="G163" s="7" t="s">
-        <v>723</v>
       </c>
       <c r="H163" s="8" t="s">
         <v>59</v>
@@ -10101,7 +10119,7 @@
       <c r="N163" s="9"/>
       <c r="O163" s="7"/>
     </row>
-    <row r="164" spans="1:15" ht="47" customHeight="1">
+    <row r="164" spans="1:15" ht="47.1" customHeight="1">
       <c r="A164" s="7">
         <v>163</v>
       </c>
@@ -10109,19 +10127,19 @@
         <v>39</v>
       </c>
       <c r="C164" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="D164" s="7" t="s">
         <v>724</v>
       </c>
-      <c r="D164" s="7" t="s">
+      <c r="E164" s="7" t="s">
         <v>725</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="F164" s="7" t="s">
         <v>726</v>
       </c>
-      <c r="F164" s="7" t="s">
+      <c r="G164" s="7" t="s">
         <v>727</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>728</v>
       </c>
       <c r="H164" s="8" t="s">
         <v>59</v>
@@ -10140,7 +10158,7 @@
       <c r="N164" s="9"/>
       <c r="O164" s="7"/>
     </row>
-    <row r="165" spans="1:15" ht="26.75" customHeight="1">
+    <row r="165" spans="1:15" ht="26.85" customHeight="1">
       <c r="A165" s="7">
         <v>164</v>
       </c>
@@ -10148,19 +10166,19 @@
         <v>39</v>
       </c>
       <c r="C165" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="D165" s="7" t="s">
         <v>729</v>
       </c>
-      <c r="D165" s="7" t="s">
+      <c r="E165" s="7" t="s">
         <v>730</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="F165" s="7" t="s">
         <v>731</v>
       </c>
-      <c r="F165" s="7" t="s">
+      <c r="G165" s="7" t="s">
         <v>732</v>
-      </c>
-      <c r="G165" s="7" t="s">
-        <v>733</v>
       </c>
       <c r="H165" s="8" t="s">
         <v>59</v>
@@ -10221,7 +10239,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -10233,21 +10251,21 @@
     <col min="8" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.75" customHeight="1">
+    <row r="1" spans="1:8" ht="26.85" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>48</v>
@@ -10259,21 +10277,21 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="47" customHeight="1">
+    <row r="2" spans="1:8" ht="47.1" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>741</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>742</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>60</v>
@@ -10282,24 +10300,24 @@
         <v>61</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.75" customHeight="1">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="26.85" customHeight="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>744</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>745</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>81</v>
@@ -10309,21 +10327,21 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="26.75" customHeight="1">
+    <row r="4" spans="1:8" ht="26.85" customHeight="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>746</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>748</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>81</v>
@@ -10333,21 +10351,21 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="26.75" customHeight="1">
+    <row r="5" spans="1:8" ht="26.85" customHeight="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>751</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>81</v>
@@ -10357,21 +10375,21 @@
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="26.75" customHeight="1">
+    <row r="6" spans="1:8" ht="26.85" customHeight="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>428</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>60</v>
@@ -10380,24 +10398,24 @@
         <v>61</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="26.75" customHeight="1">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="26.85" customHeight="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>754</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>755</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>81</v>
@@ -10407,21 +10425,21 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="26.75" customHeight="1">
+    <row r="8" spans="1:8" ht="26.85" customHeight="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>758</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>759</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>60</v>
@@ -10430,24 +10448,24 @@
         <v>61</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="26.75" customHeight="1">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="26.85" customHeight="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>761</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>762</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>60</v>
@@ -10456,24 +10474,24 @@
         <v>61</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="26.75" customHeight="1">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="26.85" customHeight="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>764</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>765</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>81</v>
@@ -10483,21 +10501,21 @@
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="26.75" customHeight="1">
+    <row r="11" spans="1:8" ht="26.85" customHeight="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>768</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>769</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>60</v>
@@ -10506,24 +10524,24 @@
         <v>61</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="26.75" customHeight="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="26.85" customHeight="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>772</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>60</v>
@@ -10532,24 +10550,24 @@
         <v>61</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="26.75" customHeight="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="26.85" customHeight="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>775</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>776</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>81</v>
@@ -10559,21 +10577,21 @@
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" ht="26.75" customHeight="1">
+    <row r="14" spans="1:8" ht="26.85" customHeight="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>778</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>779</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>81</v>
@@ -10583,21 +10601,21 @@
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" ht="26.75" customHeight="1">
+    <row r="15" spans="1:8" ht="26.85" customHeight="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>782</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>783</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>81</v>
@@ -10607,21 +10625,21 @@
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="26.75" customHeight="1">
+    <row r="16" spans="1:8" ht="26.85" customHeight="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>785</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>786</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>81</v>
@@ -10631,21 +10649,21 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="26.75" customHeight="1">
+    <row r="17" spans="1:8" ht="26.85" customHeight="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>789</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>790</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>81</v>
@@ -10655,21 +10673,21 @@
       </c>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" ht="26.75" customHeight="1">
+    <row r="18" spans="1:8" ht="26.85" customHeight="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>793</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>81</v>
@@ -10709,64 +10727,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="34" customHeight="1">
+    <row r="1" spans="1:1" ht="33.950000000000003" customHeight="1">
       <c r="A1" s="10" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="3" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A4" s="4" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A9" s="4" t="s">
+    <row r="10" spans="1:1" ht="26.85" customHeight="1">
+      <c r="A10" s="4" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="26.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
         <v>803</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="18">
-      <c r="A11" s="1" t="s">
-        <v>804</v>
       </c>
     </row>
   </sheetData>
